--- a/BCAIII_2026-27.xlsx
+++ b/BCAIII_2026-27.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10916"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C9FDD76-C9DB-0147-9DF4-29A50FDD11EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5A45917-9AC2-4F4F-A001-33AC3304E268}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="20480" windowHeight="13160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="884" uniqueCount="356">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="890" uniqueCount="359">
   <si>
     <t>Enroll. No</t>
   </si>
@@ -1111,6 +1111,15 @@
   <si>
     <t>19.8.26</t>
   </si>
+  <si>
+    <t>20.8.26</t>
+  </si>
+  <si>
+    <t>21.8.2</t>
+  </si>
+  <si>
+    <t>21.8.26</t>
+  </si>
 </sst>
 </file>
 
@@ -2098,9 +2107,9 @@
   <cols>
     <col min="2" max="3" width="19.33203125" customWidth="1"/>
     <col min="4" max="4" width="7.33203125" customWidth="1"/>
-    <col min="5" max="5" width="5" customWidth="1"/>
-    <col min="6" max="13" width="8.83203125" hidden="1" customWidth="1"/>
-    <col min="14" max="61" width="8.83203125" customWidth="1"/>
+    <col min="5" max="5" width="5" hidden="1" customWidth="1"/>
+    <col min="6" max="15" width="8.83203125" hidden="1" customWidth="1"/>
+    <col min="16" max="61" width="8.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:62" x14ac:dyDescent="0.2">
@@ -2185,6 +2194,12 @@
       </c>
       <c r="T5" t="s">
         <v>355</v>
+      </c>
+      <c r="U5" t="s">
+        <v>356</v>
+      </c>
+      <c r="V5" t="s">
+        <v>357</v>
       </c>
     </row>
     <row r="6" spans="1:62" ht="24" x14ac:dyDescent="0.2">
@@ -2380,10 +2395,10 @@
         <v>1</v>
       </c>
       <c r="U7" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V7" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W7" s="4" t="b">
         <v>0</v>
@@ -2504,7 +2519,7 @@
       </c>
       <c r="BJ7">
         <f>COUNTIF(F7:BI7, TRUE)</f>
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:62" ht="35" customHeight="1" x14ac:dyDescent="0.25">
@@ -2647,10 +2662,10 @@
         <v>1</v>
       </c>
       <c r="U9" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V9" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W9" s="4" t="b">
         <v>0</v>
@@ -2771,7 +2786,7 @@
       </c>
       <c r="BJ9" s="5">
         <f t="shared" ref="BJ9:BJ58" si="0">COUNTIF(F9:BI9, TRUE)/$BJ$7</f>
-        <v>0.7857142857142857</v>
+        <v>0.8125</v>
       </c>
     </row>
     <row r="10" spans="1:62" ht="35" customHeight="1" x14ac:dyDescent="0.2">
@@ -2836,10 +2851,10 @@
         <v>1</v>
       </c>
       <c r="U10" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V10" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W10" s="4" t="b">
         <v>0</v>
@@ -2960,7 +2975,7 @@
       </c>
       <c r="BJ10" s="5">
         <f t="shared" si="0"/>
-        <v>0.7857142857142857</v>
+        <v>0.8125</v>
       </c>
     </row>
     <row r="11" spans="1:62" ht="35" customHeight="1" x14ac:dyDescent="0.2">
@@ -3025,10 +3040,10 @@
         <v>1</v>
       </c>
       <c r="U11" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V11" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W11" s="4" t="b">
         <v>0</v>
@@ -3149,7 +3164,7 @@
       </c>
       <c r="BJ11" s="5">
         <f t="shared" si="0"/>
-        <v>0.7142857142857143</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="12" spans="1:62" ht="35" customHeight="1" x14ac:dyDescent="0.2">
@@ -3214,10 +3229,10 @@
         <v>1</v>
       </c>
       <c r="U12" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V12" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W12" s="4" t="b">
         <v>0</v>
@@ -3403,7 +3418,7 @@
         <v>1</v>
       </c>
       <c r="U13" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V13" s="4" t="b">
         <v>0</v>
@@ -3527,7 +3542,7 @@
       </c>
       <c r="BJ13" s="5">
         <f t="shared" si="0"/>
-        <v>0.8571428571428571</v>
+        <v>0.8125</v>
       </c>
     </row>
     <row r="14" spans="1:62" ht="35" customHeight="1" x14ac:dyDescent="0.2">
@@ -3592,10 +3607,10 @@
         <v>1</v>
       </c>
       <c r="U14" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V14" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W14" s="4" t="b">
         <v>0</v>
@@ -3905,7 +3920,7 @@
       </c>
       <c r="BJ15" s="5">
         <f t="shared" si="0"/>
-        <v>0.8571428571428571</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="16" spans="1:62" ht="35" customHeight="1" x14ac:dyDescent="0.2">
@@ -3970,10 +3985,10 @@
         <v>1</v>
       </c>
       <c r="U16" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V16" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W16" s="4" t="b">
         <v>0</v>
@@ -4094,7 +4109,7 @@
       </c>
       <c r="BJ16" s="5">
         <f t="shared" si="0"/>
-        <v>0.7142857142857143</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="17" spans="1:62" ht="35" customHeight="1" x14ac:dyDescent="0.2">
@@ -4159,10 +4174,10 @@
         <v>1</v>
       </c>
       <c r="U17" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V17" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W17" s="4" t="b">
         <v>0</v>
@@ -4283,7 +4298,7 @@
       </c>
       <c r="BJ17" s="5">
         <f t="shared" si="0"/>
-        <v>0.8571428571428571</v>
+        <v>0.875</v>
       </c>
     </row>
     <row r="18" spans="1:62" ht="35" customHeight="1" x14ac:dyDescent="0.2">
@@ -4348,10 +4363,10 @@
         <v>1</v>
       </c>
       <c r="U18" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V18" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W18" s="4" t="b">
         <v>0</v>
@@ -4472,7 +4487,7 @@
       </c>
       <c r="BJ18" s="5">
         <f t="shared" si="0"/>
-        <v>0.6428571428571429</v>
+        <v>0.6875</v>
       </c>
     </row>
     <row r="19" spans="1:62" s="10" customFormat="1" ht="35" customHeight="1" x14ac:dyDescent="0.2">
@@ -4537,10 +4552,10 @@
         <v>1</v>
       </c>
       <c r="U19" s="12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V19" s="12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W19" s="12" t="b">
         <v>0</v>
@@ -4726,10 +4741,10 @@
         <v>1</v>
       </c>
       <c r="U20" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V20" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W20" s="4" t="b">
         <v>0</v>
@@ -4850,7 +4865,7 @@
       </c>
       <c r="BJ20" s="5">
         <f t="shared" si="0"/>
-        <v>0.7142857142857143</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="21" spans="1:62" ht="35" customHeight="1" x14ac:dyDescent="0.2">
@@ -4915,10 +4930,10 @@
         <v>1</v>
       </c>
       <c r="U21" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V21" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W21" s="4" t="b">
         <v>0</v>
@@ -5039,7 +5054,7 @@
       </c>
       <c r="BJ21" s="5">
         <f t="shared" si="0"/>
-        <v>0.7142857142857143</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="22" spans="1:62" ht="35" customHeight="1" x14ac:dyDescent="0.2">
@@ -5104,10 +5119,10 @@
         <v>0</v>
       </c>
       <c r="U22" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V22" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W22" s="4" t="b">
         <v>0</v>
@@ -5228,7 +5243,7 @@
       </c>
       <c r="BJ22" s="5">
         <f t="shared" si="0"/>
-        <v>0.42857142857142855</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="23" spans="1:62" ht="35" customHeight="1" x14ac:dyDescent="0.2">
@@ -5293,10 +5308,10 @@
         <v>1</v>
       </c>
       <c r="U23" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V23" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W23" s="4" t="b">
         <v>0</v>
@@ -5417,7 +5432,7 @@
       </c>
       <c r="BJ23" s="5">
         <f t="shared" si="0"/>
-        <v>0.7142857142857143</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="24" spans="1:62" ht="35" customHeight="1" x14ac:dyDescent="0.2">
@@ -5485,7 +5500,7 @@
         <v>0</v>
       </c>
       <c r="V24" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W24" s="4" t="b">
         <v>0</v>
@@ -5606,7 +5621,7 @@
       </c>
       <c r="BJ24" s="5">
         <f t="shared" si="0"/>
-        <v>0.7857142857142857</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="25" spans="1:62" ht="35" customHeight="1" x14ac:dyDescent="0.2">
@@ -5671,10 +5686,10 @@
         <v>1</v>
       </c>
       <c r="U25" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V25" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W25" s="4" t="b">
         <v>0</v>
@@ -5795,7 +5810,7 @@
       </c>
       <c r="BJ25" s="5">
         <f t="shared" si="0"/>
-        <v>0.5714285714285714</v>
+        <v>0.625</v>
       </c>
     </row>
     <row r="26" spans="1:62" ht="35" customHeight="1" x14ac:dyDescent="0.2">
@@ -5860,10 +5875,10 @@
         <v>1</v>
       </c>
       <c r="U26" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V26" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W26" s="4" t="b">
         <v>0</v>
@@ -5984,7 +5999,7 @@
       </c>
       <c r="BJ26" s="5">
         <f t="shared" si="0"/>
-        <v>0.9285714285714286</v>
+        <v>0.9375</v>
       </c>
     </row>
     <row r="27" spans="1:62" ht="35" customHeight="1" x14ac:dyDescent="0.2">
@@ -6049,10 +6064,10 @@
         <v>1</v>
       </c>
       <c r="U27" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V27" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W27" s="4" t="b">
         <v>0</v>
@@ -6173,7 +6188,7 @@
       </c>
       <c r="BJ27" s="5">
         <f t="shared" si="0"/>
-        <v>0.5714285714285714</v>
+        <v>0.625</v>
       </c>
     </row>
     <row r="28" spans="1:62" ht="35" customHeight="1" x14ac:dyDescent="0.2">
@@ -6238,10 +6253,10 @@
         <v>1</v>
       </c>
       <c r="U28" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V28" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W28" s="4" t="b">
         <v>0</v>
@@ -6362,7 +6377,7 @@
       </c>
       <c r="BJ28" s="5">
         <f t="shared" si="0"/>
-        <v>0.8571428571428571</v>
+        <v>0.875</v>
       </c>
     </row>
     <row r="29" spans="1:62" ht="35" customHeight="1" x14ac:dyDescent="0.2">
@@ -6427,10 +6442,10 @@
         <v>1</v>
       </c>
       <c r="U29" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V29" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W29" s="4" t="b">
         <v>0</v>
@@ -6551,7 +6566,7 @@
       </c>
       <c r="BJ29" s="5">
         <f t="shared" si="0"/>
-        <v>0.5714285714285714</v>
+        <v>0.625</v>
       </c>
     </row>
     <row r="30" spans="1:62" ht="35" customHeight="1" x14ac:dyDescent="0.2">
@@ -6616,10 +6631,10 @@
         <v>1</v>
       </c>
       <c r="U30" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V30" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W30" s="4" t="b">
         <v>0</v>
@@ -6740,7 +6755,7 @@
       </c>
       <c r="BJ30" s="5">
         <f t="shared" si="0"/>
-        <v>0.9285714285714286</v>
+        <v>0.9375</v>
       </c>
     </row>
     <row r="31" spans="1:62" ht="35" customHeight="1" x14ac:dyDescent="0.2">
@@ -6805,10 +6820,10 @@
         <v>0</v>
       </c>
       <c r="U31" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V31" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W31" s="4" t="b">
         <v>0</v>
@@ -6929,7 +6944,7 @@
       </c>
       <c r="BJ31" s="5">
         <f t="shared" si="0"/>
-        <v>0.7857142857142857</v>
+        <v>0.8125</v>
       </c>
     </row>
     <row r="32" spans="1:62" ht="35" customHeight="1" x14ac:dyDescent="0.2">
@@ -7118,7 +7133,7 @@
       </c>
       <c r="BJ32" s="5">
         <f t="shared" si="0"/>
-        <v>0.5714285714285714</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="33" spans="1:64" ht="35" customHeight="1" x14ac:dyDescent="0.2">
@@ -7183,10 +7198,10 @@
         <v>1</v>
       </c>
       <c r="U33" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V33" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W33" s="4" t="b">
         <v>0</v>
@@ -7307,7 +7322,7 @@
       </c>
       <c r="BJ33" s="5">
         <f t="shared" si="0"/>
-        <v>0.7857142857142857</v>
+        <v>0.8125</v>
       </c>
     </row>
     <row r="34" spans="1:64" ht="35" customHeight="1" x14ac:dyDescent="0.2">
@@ -7372,10 +7387,10 @@
         <v>1</v>
       </c>
       <c r="U34" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V34" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W34" s="4" t="b">
         <v>0</v>
@@ -7496,7 +7511,7 @@
       </c>
       <c r="BJ34" s="5">
         <f t="shared" si="0"/>
-        <v>0.9285714285714286</v>
+        <v>0.9375</v>
       </c>
     </row>
     <row r="35" spans="1:64" ht="35" customHeight="1" x14ac:dyDescent="0.2">
@@ -7561,10 +7576,10 @@
         <v>1</v>
       </c>
       <c r="U35" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V35" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W35" s="4" t="b">
         <v>0</v>
@@ -7750,10 +7765,10 @@
         <v>1</v>
       </c>
       <c r="U36" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V36" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W36" s="4" t="b">
         <v>0</v>
@@ -7874,7 +7889,7 @@
       </c>
       <c r="BJ36" s="5">
         <f t="shared" si="0"/>
-        <v>0.9285714285714286</v>
+        <v>0.9375</v>
       </c>
     </row>
     <row r="37" spans="1:64" ht="35" customHeight="1" x14ac:dyDescent="0.2">
@@ -7942,7 +7957,7 @@
         <v>0</v>
       </c>
       <c r="V37" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W37" s="4" t="b">
         <v>0</v>
@@ -8063,11 +8078,11 @@
       </c>
       <c r="BJ37" s="5">
         <f t="shared" si="0"/>
-        <v>0.7857142857142857</v>
+        <v>0.75</v>
       </c>
       <c r="BL37">
         <f>COUNTIF(F37:AR37,TRUE)</f>
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="38" spans="1:64" ht="35" customHeight="1" x14ac:dyDescent="0.2">
@@ -8135,7 +8150,7 @@
         <v>0</v>
       </c>
       <c r="V38" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W38" s="4" t="b">
         <v>0</v>
@@ -8256,7 +8271,7 @@
       </c>
       <c r="BJ38" s="5">
         <f t="shared" si="0"/>
-        <v>0.5714285714285714</v>
+        <v>0.5625</v>
       </c>
     </row>
     <row r="39" spans="1:64" ht="35" customHeight="1" x14ac:dyDescent="0.2">
@@ -8321,7 +8336,7 @@
         <v>0</v>
       </c>
       <c r="U39" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V39" s="4" t="b">
         <v>0</v>
@@ -8445,7 +8460,7 @@
       </c>
       <c r="BJ39" s="5">
         <f t="shared" si="0"/>
-        <v>0.5714285714285714</v>
+        <v>0.5625</v>
       </c>
     </row>
     <row r="40" spans="1:64" ht="35" customHeight="1" x14ac:dyDescent="0.2">
@@ -8510,10 +8525,10 @@
         <v>0</v>
       </c>
       <c r="U40" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V40" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W40" s="4" t="b">
         <v>0</v>
@@ -8634,7 +8649,7 @@
       </c>
       <c r="BJ40" s="5">
         <f t="shared" si="0"/>
-        <v>0.7857142857142857</v>
+        <v>0.8125</v>
       </c>
     </row>
     <row r="41" spans="1:64" ht="35" customHeight="1" x14ac:dyDescent="0.2">
@@ -8702,7 +8717,7 @@
         <v>0</v>
       </c>
       <c r="V41" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W41" s="4" t="b">
         <v>0</v>
@@ -8823,11 +8838,11 @@
       </c>
       <c r="BJ41" s="5">
         <f t="shared" si="0"/>
-        <v>0.7142857142857143</v>
+        <v>0.6875</v>
       </c>
       <c r="BL41">
         <f>COUNTIF(F41:BI41,TRUE)</f>
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="42" spans="1:64" ht="35" customHeight="1" x14ac:dyDescent="0.2">
@@ -8892,10 +8907,10 @@
         <v>1</v>
       </c>
       <c r="U42" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V42" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W42" s="4" t="b">
         <v>0</v>
@@ -9016,7 +9031,7 @@
       </c>
       <c r="BJ42" s="5">
         <f t="shared" si="0"/>
-        <v>0.9285714285714286</v>
+        <v>0.9375</v>
       </c>
     </row>
     <row r="43" spans="1:64" ht="35" customHeight="1" x14ac:dyDescent="0.2">
@@ -9081,10 +9096,10 @@
         <v>1</v>
       </c>
       <c r="U43" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V43" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W43" s="4" t="b">
         <v>0</v>
@@ -9205,7 +9220,7 @@
       </c>
       <c r="BJ43" s="5">
         <f t="shared" si="0"/>
-        <v>0.8571428571428571</v>
+        <v>0.875</v>
       </c>
     </row>
     <row r="44" spans="1:64" ht="35" customHeight="1" x14ac:dyDescent="0.2">
@@ -9270,7 +9285,7 @@
         <v>1</v>
       </c>
       <c r="U44" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V44" s="4" t="b">
         <v>0</v>
@@ -9394,7 +9409,7 @@
       </c>
       <c r="BJ44" s="5">
         <f t="shared" si="0"/>
-        <v>0.8571428571428571</v>
+        <v>0.8125</v>
       </c>
     </row>
     <row r="45" spans="1:64" ht="35" customHeight="1" x14ac:dyDescent="0.2">
@@ -9459,10 +9474,10 @@
         <v>1</v>
       </c>
       <c r="U45" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V45" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W45" s="4" t="b">
         <v>0</v>
@@ -9583,7 +9598,7 @@
       </c>
       <c r="BJ45" s="5">
         <f t="shared" si="0"/>
-        <v>0.8571428571428571</v>
+        <v>0.875</v>
       </c>
     </row>
     <row r="46" spans="1:64" ht="35" customHeight="1" x14ac:dyDescent="0.2">
@@ -9648,10 +9663,10 @@
         <v>1</v>
       </c>
       <c r="U46" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V46" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W46" s="4" t="b">
         <v>0</v>
@@ -9772,7 +9787,7 @@
       </c>
       <c r="BJ46" s="5">
         <f t="shared" si="0"/>
-        <v>0.7857142857142857</v>
+        <v>0.8125</v>
       </c>
     </row>
     <row r="47" spans="1:64" ht="35" customHeight="1" x14ac:dyDescent="0.2">
@@ -9837,7 +9852,7 @@
         <v>1</v>
       </c>
       <c r="U47" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V47" s="4" t="b">
         <v>0</v>
@@ -9961,7 +9976,7 @@
       </c>
       <c r="BJ47" s="5">
         <f t="shared" si="0"/>
-        <v>0.8571428571428571</v>
+        <v>0.8125</v>
       </c>
     </row>
     <row r="48" spans="1:64" ht="35" customHeight="1" x14ac:dyDescent="0.2">
@@ -10026,10 +10041,10 @@
         <v>1</v>
       </c>
       <c r="U48" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V48" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W48" s="4" t="b">
         <v>0</v>
@@ -10150,7 +10165,7 @@
       </c>
       <c r="BJ48" s="5">
         <f t="shared" si="0"/>
-        <v>0.6428571428571429</v>
+        <v>0.6875</v>
       </c>
     </row>
     <row r="49" spans="1:64" ht="35" customHeight="1" x14ac:dyDescent="0.2">
@@ -10215,10 +10230,10 @@
         <v>1</v>
       </c>
       <c r="U49" s="8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V49" s="8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W49" s="8" t="b">
         <v>0</v>
@@ -10339,7 +10354,7 @@
       </c>
       <c r="BJ49" s="9">
         <f t="shared" si="0"/>
-        <v>0.8571428571428571</v>
+        <v>0.875</v>
       </c>
     </row>
     <row r="50" spans="1:64" ht="40" customHeight="1" x14ac:dyDescent="0.2">
@@ -10404,10 +10419,10 @@
         <v>0</v>
       </c>
       <c r="U50" s="8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V50" s="8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W50" s="8" t="b">
         <v>0</v>
@@ -10528,11 +10543,11 @@
       </c>
       <c r="BJ50" s="9">
         <f t="shared" si="0"/>
-        <v>0.8571428571428571</v>
+        <v>0.875</v>
       </c>
       <c r="BL50">
         <f>COUNTIF(F50:BI50,TRUE)</f>
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="51" spans="1:64" ht="90" x14ac:dyDescent="0.2">
@@ -10597,10 +10612,10 @@
         <v>0</v>
       </c>
       <c r="U51" s="8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V51" s="8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W51" s="8" t="b">
         <v>0</v>
@@ -10721,7 +10736,7 @@
       </c>
       <c r="BJ51" s="9">
         <f t="shared" si="0"/>
-        <v>0.7142857142857143</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="52" spans="1:64" ht="90" x14ac:dyDescent="0.2">
@@ -10786,10 +10801,10 @@
         <v>1</v>
       </c>
       <c r="U52" s="8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V52" s="8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W52" s="8" t="b">
         <v>0</v>
@@ -10975,7 +10990,7 @@
         <v>1</v>
       </c>
       <c r="U53" s="8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V53" s="8" t="b">
         <v>0</v>
@@ -11099,7 +11114,7 @@
       </c>
       <c r="BJ53" s="9">
         <f t="shared" si="0"/>
-        <v>0.6428571428571429</v>
+        <v>0.625</v>
       </c>
     </row>
     <row r="54" spans="1:64" x14ac:dyDescent="0.2">
@@ -11164,10 +11179,10 @@
         <v>1</v>
       </c>
       <c r="U54" s="8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V54" s="8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W54" s="8" t="b">
         <v>0</v>
@@ -11353,10 +11368,10 @@
         <v>1</v>
       </c>
       <c r="U55" s="8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V55" s="8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W55" s="8" t="b">
         <v>0</v>
@@ -11542,10 +11557,10 @@
         <v>1</v>
       </c>
       <c r="U56" s="8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V56" s="8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W56" s="8" t="b">
         <v>0</v>
@@ -11734,7 +11749,7 @@
         <v>0</v>
       </c>
       <c r="V57" s="8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W57" s="8" t="b">
         <v>0</v>
@@ -11855,7 +11870,7 @@
       </c>
       <c r="BJ57" s="9">
         <f t="shared" si="0"/>
-        <v>0.8571428571428571</v>
+        <v>0.8125</v>
       </c>
     </row>
     <row r="58" spans="1:64" x14ac:dyDescent="0.2">
@@ -11920,10 +11935,10 @@
         <v>1</v>
       </c>
       <c r="U58" s="8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V58" s="8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W58" s="8" t="b">
         <v>0</v>
@@ -12044,7 +12059,7 @@
       </c>
       <c r="BJ58" s="9">
         <f t="shared" si="0"/>
-        <v>0.8571428571428571</v>
+        <v>0.875</v>
       </c>
     </row>
     <row r="59" spans="1:64" x14ac:dyDescent="0.2">
@@ -12110,11 +12125,11 @@
       </c>
       <c r="U59">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="V59">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="W59">
         <f t="shared" si="1"/>
@@ -12336,11 +12351,11 @@
       </c>
       <c r="U60">
         <f t="shared" si="3"/>
-        <v>42</v>
+        <v>6</v>
       </c>
       <c r="V60">
         <f t="shared" si="3"/>
-        <v>42</v>
+        <v>6</v>
       </c>
       <c r="W60">
         <f t="shared" si="3"/>
@@ -12597,8 +12612,8 @@
     <col min="3" max="3" width="17.33203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="7.5" customWidth="1"/>
     <col min="5" max="5" width="5.33203125" customWidth="1"/>
-    <col min="6" max="12" width="8.83203125" hidden="1" customWidth="1"/>
-    <col min="13" max="62" width="8.83203125" customWidth="1"/>
+    <col min="6" max="18" width="8.83203125" hidden="1" customWidth="1"/>
+    <col min="19" max="62" width="8.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:63" x14ac:dyDescent="0.2">
@@ -12680,6 +12695,12 @@
       </c>
       <c r="T5" t="s">
         <v>355</v>
+      </c>
+      <c r="U5" t="s">
+        <v>356</v>
+      </c>
+      <c r="V5" t="s">
+        <v>358</v>
       </c>
     </row>
     <row r="6" spans="1:63" ht="24" x14ac:dyDescent="0.2">
@@ -12876,10 +12897,10 @@
         <v>1</v>
       </c>
       <c r="U7" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V7" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W7" s="4" t="b">
         <v>0</v>
@@ -13003,7 +13024,7 @@
       </c>
       <c r="BK7">
         <f>COUNTIF(F7:BJ7, TRUE)</f>
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:63" ht="35" customHeight="1" x14ac:dyDescent="0.25">
@@ -13145,10 +13166,10 @@
         <v>1</v>
       </c>
       <c r="U9" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V9" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W9" s="4" t="b">
         <v>0</v>
@@ -13272,7 +13293,7 @@
       </c>
       <c r="BK9" s="5">
         <f t="shared" ref="BK9:BK58" si="0">COUNTIF(F9:BJ9, TRUE)/$BK$7</f>
-        <v>0.8571428571428571</v>
+        <v>0.875</v>
       </c>
     </row>
     <row r="10" spans="1:63" ht="35" customHeight="1" x14ac:dyDescent="0.2">
@@ -13337,7 +13358,7 @@
         <v>1</v>
       </c>
       <c r="U10" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V10" s="4" t="b">
         <v>0</v>
@@ -13464,7 +13485,7 @@
       </c>
       <c r="BK10" s="5">
         <f t="shared" si="0"/>
-        <v>0.6428571428571429</v>
+        <v>0.625</v>
       </c>
     </row>
     <row r="11" spans="1:63" ht="35" customHeight="1" x14ac:dyDescent="0.2">
@@ -13532,7 +13553,7 @@
         <v>0</v>
       </c>
       <c r="V11" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W11" s="4" t="b">
         <v>0</v>
@@ -13656,7 +13677,7 @@
       </c>
       <c r="BK11" s="5">
         <f t="shared" si="0"/>
-        <v>0.5714285714285714</v>
+        <v>0.5625</v>
       </c>
     </row>
     <row r="12" spans="1:63" ht="35" customHeight="1" x14ac:dyDescent="0.2">
@@ -13721,7 +13742,7 @@
         <v>1</v>
       </c>
       <c r="U12" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V12" s="4" t="b">
         <v>0</v>
@@ -13848,7 +13869,7 @@
       </c>
       <c r="BK12" s="5">
         <f t="shared" si="0"/>
-        <v>0.9285714285714286</v>
+        <v>0.875</v>
       </c>
     </row>
     <row r="13" spans="1:63" ht="35" customHeight="1" x14ac:dyDescent="0.2">
@@ -13913,10 +13934,10 @@
         <v>1</v>
       </c>
       <c r="U13" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V13" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W13" s="4" t="b">
         <v>0</v>
@@ -14040,7 +14061,7 @@
       </c>
       <c r="BK13" s="5">
         <f t="shared" si="0"/>
-        <v>0.9285714285714286</v>
+        <v>0.9375</v>
       </c>
     </row>
     <row r="14" spans="1:63" ht="35" customHeight="1" x14ac:dyDescent="0.2">
@@ -14108,7 +14129,7 @@
         <v>0</v>
       </c>
       <c r="V14" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W14" s="4" t="b">
         <v>0</v>
@@ -14232,7 +14253,7 @@
       </c>
       <c r="BK14" s="5">
         <f t="shared" si="0"/>
-        <v>0.8571428571428571</v>
+        <v>0.8125</v>
       </c>
     </row>
     <row r="15" spans="1:63" ht="35" customHeight="1" x14ac:dyDescent="0.2">
@@ -14297,10 +14318,10 @@
         <v>1</v>
       </c>
       <c r="U15" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V15" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W15" s="4" t="b">
         <v>0</v>
@@ -14424,7 +14445,7 @@
       </c>
       <c r="BK15" s="5">
         <f t="shared" si="0"/>
-        <v>0.7142857142857143</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="16" spans="1:63" ht="35" customHeight="1" x14ac:dyDescent="0.2">
@@ -14489,10 +14510,10 @@
         <v>0</v>
       </c>
       <c r="U16" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V16" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W16" s="4" t="b">
         <v>0</v>
@@ -14616,7 +14637,7 @@
       </c>
       <c r="BK16" s="5">
         <f t="shared" si="0"/>
-        <v>0.7857142857142857</v>
+        <v>0.8125</v>
       </c>
     </row>
     <row r="17" spans="1:63" ht="35" customHeight="1" x14ac:dyDescent="0.2">
@@ -14681,10 +14702,10 @@
         <v>1</v>
       </c>
       <c r="U17" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V17" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W17" s="4" t="b">
         <v>0</v>
@@ -14808,7 +14829,7 @@
       </c>
       <c r="BK17" s="5">
         <f t="shared" si="0"/>
-        <v>0.9285714285714286</v>
+        <v>0.9375</v>
       </c>
     </row>
     <row r="18" spans="1:63" ht="35" customHeight="1" x14ac:dyDescent="0.2">
@@ -14873,10 +14894,10 @@
         <v>1</v>
       </c>
       <c r="U18" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V18" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W18" s="4" t="b">
         <v>0</v>
@@ -15000,7 +15021,7 @@
       </c>
       <c r="BK18" s="5">
         <f t="shared" si="0"/>
-        <v>0.8571428571428571</v>
+        <v>0.875</v>
       </c>
     </row>
     <row r="19" spans="1:63" s="10" customFormat="1" ht="35" customHeight="1" x14ac:dyDescent="0.2">
@@ -15065,10 +15086,10 @@
         <v>1</v>
       </c>
       <c r="U19" s="12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V19" s="12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W19" s="12" t="b">
         <v>0</v>
@@ -15192,7 +15213,7 @@
       </c>
       <c r="BK19" s="13">
         <f t="shared" si="0"/>
-        <v>0.9285714285714286</v>
+        <v>0.9375</v>
       </c>
     </row>
     <row r="20" spans="1:63" ht="35" customHeight="1" x14ac:dyDescent="0.2">
@@ -15257,10 +15278,10 @@
         <v>0</v>
       </c>
       <c r="U20" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V20" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W20" s="4" t="b">
         <v>0</v>
@@ -15384,7 +15405,7 @@
       </c>
       <c r="BK20" s="5">
         <f t="shared" si="0"/>
-        <v>0.6428571428571429</v>
+        <v>0.6875</v>
       </c>
     </row>
     <row r="21" spans="1:63" ht="35" customHeight="1" x14ac:dyDescent="0.2">
@@ -15452,7 +15473,7 @@
         <v>0</v>
       </c>
       <c r="V21" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W21" s="4" t="b">
         <v>0</v>
@@ -15576,7 +15597,7 @@
       </c>
       <c r="BK21" s="5">
         <f t="shared" si="0"/>
-        <v>0.8571428571428571</v>
+        <v>0.8125</v>
       </c>
     </row>
     <row r="22" spans="1:63" ht="35" customHeight="1" x14ac:dyDescent="0.2">
@@ -15644,7 +15665,7 @@
         <v>0</v>
       </c>
       <c r="V22" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W22" s="4" t="b">
         <v>0</v>
@@ -15768,7 +15789,7 @@
       </c>
       <c r="BK22" s="5">
         <f t="shared" si="0"/>
-        <v>0.42857142857142855</v>
+        <v>0.4375</v>
       </c>
     </row>
     <row r="23" spans="1:63" ht="35" customHeight="1" x14ac:dyDescent="0.2">
@@ -15833,10 +15854,10 @@
         <v>1</v>
       </c>
       <c r="U23" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V23" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W23" s="4" t="b">
         <v>0</v>
@@ -15960,7 +15981,7 @@
       </c>
       <c r="BK23" s="5">
         <f t="shared" si="0"/>
-        <v>0.9285714285714286</v>
+        <v>0.9375</v>
       </c>
     </row>
     <row r="24" spans="1:63" ht="35" customHeight="1" x14ac:dyDescent="0.2">
@@ -16025,10 +16046,10 @@
         <v>0</v>
       </c>
       <c r="U24" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V24" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W24" s="4" t="b">
         <v>0</v>
@@ -16152,7 +16173,7 @@
       </c>
       <c r="BK24" s="5">
         <f t="shared" si="0"/>
-        <v>0.35714285714285715</v>
+        <v>0.4375</v>
       </c>
     </row>
     <row r="25" spans="1:63" ht="35" customHeight="1" x14ac:dyDescent="0.2">
@@ -16217,10 +16238,10 @@
         <v>0</v>
       </c>
       <c r="U25" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V25" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W25" s="4" t="b">
         <v>0</v>
@@ -16344,7 +16365,7 @@
       </c>
       <c r="BK25" s="5">
         <f t="shared" si="0"/>
-        <v>0.35714285714285715</v>
+        <v>0.4375</v>
       </c>
     </row>
     <row r="26" spans="1:63" ht="35" customHeight="1" x14ac:dyDescent="0.2">
@@ -16409,10 +16430,10 @@
         <v>1</v>
       </c>
       <c r="U26" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V26" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W26" s="4" t="b">
         <v>0</v>
@@ -16536,7 +16557,7 @@
       </c>
       <c r="BK26" s="5">
         <f t="shared" si="0"/>
-        <v>0.8571428571428571</v>
+        <v>0.875</v>
       </c>
     </row>
     <row r="27" spans="1:63" ht="35" customHeight="1" x14ac:dyDescent="0.2">
@@ -16604,7 +16625,7 @@
         <v>0</v>
       </c>
       <c r="V27" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W27" s="4" t="b">
         <v>0</v>
@@ -16728,7 +16749,7 @@
       </c>
       <c r="BK27" s="5">
         <f t="shared" si="0"/>
-        <v>0.5714285714285714</v>
+        <v>0.5625</v>
       </c>
     </row>
     <row r="28" spans="1:63" ht="35" customHeight="1" x14ac:dyDescent="0.2">
@@ -16920,7 +16941,7 @@
       </c>
       <c r="BK28" s="5">
         <f t="shared" si="0"/>
-        <v>0.7857142857142857</v>
+        <v>0.6875</v>
       </c>
     </row>
     <row r="29" spans="1:63" ht="35" customHeight="1" x14ac:dyDescent="0.2">
@@ -17112,7 +17133,7 @@
       </c>
       <c r="BK29" s="5">
         <f t="shared" si="0"/>
-        <v>0.8571428571428571</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="30" spans="1:63" ht="35" customHeight="1" x14ac:dyDescent="0.2">
@@ -17304,7 +17325,7 @@
       </c>
       <c r="BK30" s="5">
         <f t="shared" si="0"/>
-        <v>0.8571428571428571</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="31" spans="1:63" ht="35" customHeight="1" x14ac:dyDescent="0.2">
@@ -17369,10 +17390,10 @@
         <v>0</v>
       </c>
       <c r="U31" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V31" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W31" s="4" t="b">
         <v>0</v>
@@ -17496,7 +17517,7 @@
       </c>
       <c r="BK31" s="5">
         <f t="shared" si="0"/>
-        <v>0.8571428571428571</v>
+        <v>0.875</v>
       </c>
     </row>
     <row r="32" spans="1:63" ht="35" customHeight="1" x14ac:dyDescent="0.2">
@@ -17561,10 +17582,10 @@
         <v>0</v>
       </c>
       <c r="U32" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V32" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W32" s="4" t="b">
         <v>0</v>
@@ -17688,7 +17709,7 @@
       </c>
       <c r="BK32" s="5">
         <f t="shared" si="0"/>
-        <v>0.7142857142857143</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="33" spans="1:65" ht="35" customHeight="1" x14ac:dyDescent="0.2">
@@ -17753,10 +17774,10 @@
         <v>1</v>
       </c>
       <c r="U33" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V33" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W33" s="4" t="b">
         <v>0</v>
@@ -17880,7 +17901,7 @@
       </c>
       <c r="BK33" s="5">
         <f t="shared" si="0"/>
-        <v>0.9285714285714286</v>
+        <v>0.9375</v>
       </c>
     </row>
     <row r="34" spans="1:65" ht="35" customHeight="1" x14ac:dyDescent="0.2">
@@ -17945,10 +17966,10 @@
         <v>1</v>
       </c>
       <c r="U34" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V34" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W34" s="4" t="b">
         <v>0</v>
@@ -18072,7 +18093,7 @@
       </c>
       <c r="BK34" s="5">
         <f t="shared" si="0"/>
-        <v>0.6428571428571429</v>
+        <v>0.6875</v>
       </c>
     </row>
     <row r="35" spans="1:65" ht="35" customHeight="1" x14ac:dyDescent="0.2">
@@ -18137,10 +18158,10 @@
         <v>1</v>
       </c>
       <c r="U35" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V35" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W35" s="4" t="b">
         <v>0</v>
@@ -18264,7 +18285,7 @@
       </c>
       <c r="BK35" s="5">
         <f t="shared" si="0"/>
-        <v>0.7142857142857143</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="36" spans="1:65" ht="35" customHeight="1" x14ac:dyDescent="0.2">
@@ -18329,7 +18350,7 @@
         <v>0</v>
       </c>
       <c r="U36" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V36" s="4" t="b">
         <v>0</v>
@@ -18456,7 +18477,7 @@
       </c>
       <c r="BK36" s="5">
         <f t="shared" si="0"/>
-        <v>0.7142857142857143</v>
+        <v>0.6875</v>
       </c>
     </row>
     <row r="37" spans="1:65" ht="35" customHeight="1" x14ac:dyDescent="0.2">
@@ -18521,10 +18542,10 @@
         <v>1</v>
       </c>
       <c r="U37" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V37" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W37" s="4" t="b">
         <v>0</v>
@@ -18648,11 +18669,11 @@
       </c>
       <c r="BK37" s="5">
         <f t="shared" si="0"/>
-        <v>0.6428571428571429</v>
+        <v>0.6875</v>
       </c>
       <c r="BM37">
         <f>COUNTIF(F37:AS37,TRUE)</f>
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="38" spans="1:65" ht="35" customHeight="1" x14ac:dyDescent="0.2">
@@ -18717,10 +18738,10 @@
         <v>1</v>
       </c>
       <c r="U38" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V38" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W38" s="4" t="b">
         <v>0</v>
@@ -18844,7 +18865,7 @@
       </c>
       <c r="BK38" s="5">
         <f t="shared" si="0"/>
-        <v>0.9285714285714286</v>
+        <v>0.9375</v>
       </c>
     </row>
     <row r="39" spans="1:65" ht="35" customHeight="1" x14ac:dyDescent="0.2">
@@ -18912,7 +18933,7 @@
         <v>0</v>
       </c>
       <c r="V39" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W39" s="4" t="b">
         <v>0</v>
@@ -19036,7 +19057,7 @@
       </c>
       <c r="BK39" s="5">
         <f t="shared" si="0"/>
-        <v>0.5714285714285714</v>
+        <v>0.5625</v>
       </c>
     </row>
     <row r="40" spans="1:65" ht="35" customHeight="1" x14ac:dyDescent="0.2">
@@ -19101,10 +19122,10 @@
         <v>1</v>
       </c>
       <c r="U40" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V40" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W40" s="4" t="b">
         <v>0</v>
@@ -19228,7 +19249,7 @@
       </c>
       <c r="BK40" s="5">
         <f t="shared" si="0"/>
-        <v>0.8571428571428571</v>
+        <v>0.875</v>
       </c>
     </row>
     <row r="41" spans="1:65" ht="35" customHeight="1" x14ac:dyDescent="0.2">
@@ -19293,10 +19314,10 @@
         <v>0</v>
       </c>
       <c r="U41" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V41" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W41" s="4" t="b">
         <v>0</v>
@@ -19420,11 +19441,11 @@
       </c>
       <c r="BK41" s="5">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0.5625</v>
       </c>
       <c r="BM41">
         <f>COUNTIF(F41:BJ41,TRUE)</f>
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="42" spans="1:65" ht="35" customHeight="1" x14ac:dyDescent="0.2">
@@ -19489,10 +19510,10 @@
         <v>1</v>
       </c>
       <c r="U42" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V42" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W42" s="4" t="b">
         <v>0</v>
@@ -19616,7 +19637,7 @@
       </c>
       <c r="BK42" s="5">
         <f t="shared" si="0"/>
-        <v>0.8571428571428571</v>
+        <v>0.875</v>
       </c>
     </row>
     <row r="43" spans="1:65" ht="35" customHeight="1" x14ac:dyDescent="0.2">
@@ -19681,10 +19702,10 @@
         <v>1</v>
       </c>
       <c r="U43" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V43" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W43" s="4" t="b">
         <v>0</v>
@@ -19808,7 +19829,7 @@
       </c>
       <c r="BK43" s="5">
         <f t="shared" si="0"/>
-        <v>0.9285714285714286</v>
+        <v>0.9375</v>
       </c>
     </row>
     <row r="44" spans="1:65" ht="35" customHeight="1" x14ac:dyDescent="0.2">
@@ -20000,7 +20021,7 @@
       </c>
       <c r="BK44" s="5">
         <f t="shared" si="0"/>
-        <v>0.7142857142857143</v>
+        <v>0.625</v>
       </c>
     </row>
     <row r="45" spans="1:65" ht="35" customHeight="1" x14ac:dyDescent="0.2">
@@ -20068,7 +20089,7 @@
         <v>0</v>
       </c>
       <c r="V45" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W45" s="4" t="b">
         <v>0</v>
@@ -20260,7 +20281,7 @@
         <v>0</v>
       </c>
       <c r="V46" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W46" s="4" t="b">
         <v>0</v>
@@ -20384,7 +20405,7 @@
       </c>
       <c r="BK46" s="5">
         <f t="shared" si="0"/>
-        <v>0.9285714285714286</v>
+        <v>0.875</v>
       </c>
     </row>
     <row r="47" spans="1:65" ht="35" customHeight="1" x14ac:dyDescent="0.2">
@@ -20452,7 +20473,7 @@
         <v>0</v>
       </c>
       <c r="V47" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W47" s="4" t="b">
         <v>0</v>
@@ -20576,7 +20597,7 @@
       </c>
       <c r="BK47" s="5">
         <f t="shared" si="0"/>
-        <v>0.7142857142857143</v>
+        <v>0.6875</v>
       </c>
     </row>
     <row r="48" spans="1:65" ht="35" customHeight="1" x14ac:dyDescent="0.2">
@@ -20641,10 +20662,10 @@
         <v>0</v>
       </c>
       <c r="U48" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V48" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W48" s="4" t="b">
         <v>0</v>
@@ -20768,7 +20789,7 @@
       </c>
       <c r="BK48" s="5">
         <f t="shared" si="0"/>
-        <v>0.7857142857142857</v>
+        <v>0.8125</v>
       </c>
     </row>
     <row r="49" spans="1:65" ht="35" customHeight="1" x14ac:dyDescent="0.2">
@@ -20833,7 +20854,7 @@
         <v>1</v>
       </c>
       <c r="U49" s="8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V49" s="8" t="b">
         <v>0</v>
@@ -20960,7 +20981,7 @@
       </c>
       <c r="BK49" s="9">
         <f t="shared" si="0"/>
-        <v>0.7857142857142857</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="50" spans="1:65" ht="40" customHeight="1" x14ac:dyDescent="0.2">
@@ -21025,10 +21046,10 @@
         <v>1</v>
       </c>
       <c r="U50" s="8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V50" s="8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W50" s="8" t="b">
         <v>0</v>
@@ -21152,11 +21173,11 @@
       </c>
       <c r="BK50" s="9">
         <f t="shared" si="0"/>
-        <v>0.9285714285714286</v>
+        <v>0.9375</v>
       </c>
       <c r="BM50">
         <f>COUNTIF(F50:BJ50,TRUE)</f>
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="51" spans="1:65" x14ac:dyDescent="0.2">
@@ -21221,10 +21242,10 @@
         <v>1</v>
       </c>
       <c r="U51" s="8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V51" s="8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W51" s="8" t="b">
         <v>0</v>
@@ -21348,7 +21369,7 @@
       </c>
       <c r="BK51" s="9">
         <f t="shared" si="0"/>
-        <v>0.9285714285714286</v>
+        <v>0.9375</v>
       </c>
     </row>
     <row r="52" spans="1:65" x14ac:dyDescent="0.2">
@@ -21413,10 +21434,10 @@
         <v>1</v>
       </c>
       <c r="U52" s="8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V52" s="8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W52" s="8" t="b">
         <v>0</v>
@@ -21540,7 +21561,7 @@
       </c>
       <c r="BK52" s="9">
         <f t="shared" si="0"/>
-        <v>0.9285714285714286</v>
+        <v>0.9375</v>
       </c>
     </row>
     <row r="53" spans="1:65" x14ac:dyDescent="0.2">
@@ -21732,7 +21753,7 @@
       </c>
       <c r="BK53" s="9">
         <f t="shared" si="0"/>
-        <v>7.1428571428571425E-2</v>
+        <v>6.25E-2</v>
       </c>
     </row>
     <row r="54" spans="1:65" x14ac:dyDescent="0.2">
@@ -21797,7 +21818,7 @@
         <v>0</v>
       </c>
       <c r="U54" s="8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V54" s="8" t="b">
         <v>0</v>
@@ -21924,7 +21945,7 @@
       </c>
       <c r="BK54" s="9">
         <f t="shared" si="0"/>
-        <v>0.7857142857142857</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="55" spans="1:65" x14ac:dyDescent="0.2">
@@ -21989,10 +22010,10 @@
         <v>1</v>
       </c>
       <c r="U55" s="8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V55" s="8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W55" s="8" t="b">
         <v>0</v>
@@ -22116,7 +22137,7 @@
       </c>
       <c r="BK55" s="9">
         <f t="shared" si="0"/>
-        <v>0.6428571428571429</v>
+        <v>0.6875</v>
       </c>
     </row>
     <row r="56" spans="1:65" x14ac:dyDescent="0.2">
@@ -22181,10 +22202,10 @@
         <v>1</v>
       </c>
       <c r="U56" s="8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V56" s="8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W56" s="8" t="b">
         <v>0</v>
@@ -22308,7 +22329,7 @@
       </c>
       <c r="BK56" s="9">
         <f t="shared" si="0"/>
-        <v>0.9285714285714286</v>
+        <v>0.9375</v>
       </c>
     </row>
     <row r="57" spans="1:65" x14ac:dyDescent="0.2">
@@ -22373,10 +22394,10 @@
         <v>0</v>
       </c>
       <c r="U57" s="8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V57" s="8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W57" s="8" t="b">
         <v>0</v>
@@ -22500,7 +22521,7 @@
       </c>
       <c r="BK57" s="9">
         <f t="shared" si="0"/>
-        <v>0.5714285714285714</v>
+        <v>0.625</v>
       </c>
     </row>
     <row r="58" spans="1:65" x14ac:dyDescent="0.2">
@@ -22565,7 +22586,7 @@
         <v>1</v>
       </c>
       <c r="U58" s="8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V58" s="8" t="b">
         <v>0</v>
@@ -22692,7 +22713,7 @@
       </c>
       <c r="BK58" s="9">
         <f t="shared" si="0"/>
-        <v>0.9285714285714286</v>
+        <v>0.875</v>
       </c>
     </row>
     <row r="59" spans="1:65" x14ac:dyDescent="0.2">
@@ -22754,11 +22775,11 @@
       </c>
       <c r="U59">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="V59">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="W59">
         <f t="shared" si="1"/>
@@ -22980,11 +23001,11 @@
       </c>
       <c r="U60">
         <f t="shared" si="2"/>
-        <v>42</v>
+        <v>13</v>
       </c>
       <c r="V60">
         <f t="shared" si="2"/>
-        <v>42</v>
+        <v>8</v>
       </c>
       <c r="W60">
         <f t="shared" si="2"/>
@@ -23232,7 +23253,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B41F0606-7A76-1E43-969A-749A897BA916}">
-  <sheetPr>
+  <sheetPr filterMode="1">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:BL63"/>
@@ -23313,6 +23334,12 @@
       </c>
       <c r="P5" t="s">
         <v>355</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>356</v>
+      </c>
+      <c r="R5" t="s">
+        <v>358</v>
       </c>
     </row>
     <row r="6" spans="1:62" ht="24" x14ac:dyDescent="0.2">
@@ -23496,10 +23523,10 @@
         <v>1</v>
       </c>
       <c r="Q7" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R7" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S7" s="4" t="b">
         <v>0</v>
@@ -23632,10 +23659,10 @@
       </c>
       <c r="BJ7">
         <f>COUNTIF(F7:BI7, TRUE)</f>
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:62" ht="35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:62" ht="35" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="23" t="s">
         <v>57</v>
       </c>
@@ -23711,7 +23738,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="9" spans="1:62" ht="35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:62" ht="35" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="25">
         <v>1</v>
       </c>
@@ -23764,7 +23791,7 @@
         <v>0</v>
       </c>
       <c r="R9" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S9" s="4" t="b">
         <v>0</v>
@@ -23897,7 +23924,7 @@
       </c>
       <c r="BJ9" s="5">
         <f t="shared" ref="BJ9:BJ51" si="0">COUNTIF(F9:BI9, TRUE)/$BJ$7</f>
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="10" spans="1:62" ht="35" customHeight="1" x14ac:dyDescent="0.2">
@@ -24086,10 +24113,10 @@
       </c>
       <c r="BJ10" s="5">
         <f t="shared" si="0"/>
-        <v>0.3</v>
+        <v>0.25</v>
       </c>
     </row>
-    <row r="11" spans="1:62" ht="35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:62" ht="35" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="25">
         <v>3</v>
       </c>
@@ -24133,16 +24160,16 @@
         <v>1</v>
       </c>
       <c r="O11" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P11" s="4" t="b">
         <v>1</v>
       </c>
       <c r="Q11" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R11" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S11" s="4" t="b">
         <v>0</v>
@@ -24275,10 +24302,10 @@
       </c>
       <c r="BJ11" s="5">
         <f t="shared" si="0"/>
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
     </row>
-    <row r="12" spans="1:62" ht="35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:62" ht="35" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="25">
         <v>4</v>
       </c>
@@ -24328,10 +24355,10 @@
         <v>1</v>
       </c>
       <c r="Q12" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R12" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S12" s="4" t="b">
         <v>0</v>
@@ -24464,10 +24491,10 @@
       </c>
       <c r="BJ12" s="5">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0.83333333333333337</v>
       </c>
     </row>
-    <row r="13" spans="1:62" ht="35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:62" ht="35" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="25">
         <v>5</v>
       </c>
@@ -24517,10 +24544,10 @@
         <v>1</v>
       </c>
       <c r="Q13" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R13" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S13" s="4" t="b">
         <v>0</v>
@@ -24653,10 +24680,10 @@
       </c>
       <c r="BJ13" s="5">
         <f t="shared" si="0"/>
-        <v>0.7</v>
+        <v>0.75</v>
       </c>
     </row>
-    <row r="14" spans="1:62" ht="35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:62" ht="35" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="25">
         <v>6</v>
       </c>
@@ -24706,10 +24733,10 @@
         <v>1</v>
       </c>
       <c r="Q14" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R14" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S14" s="4" t="b">
         <v>0</v>
@@ -24842,10 +24869,10 @@
       </c>
       <c r="BJ14" s="5">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0.83333333333333337</v>
       </c>
     </row>
-    <row r="15" spans="1:62" ht="35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:62" ht="35" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="25">
         <v>7</v>
       </c>
@@ -24895,10 +24922,10 @@
         <v>1</v>
       </c>
       <c r="Q15" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R15" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S15" s="4" t="b">
         <v>0</v>
@@ -25031,7 +25058,7 @@
       </c>
       <c r="BJ15" s="5">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0.83333333333333337</v>
       </c>
     </row>
     <row r="16" spans="1:62" ht="35" customHeight="1" x14ac:dyDescent="0.2">
@@ -25220,10 +25247,10 @@
       </c>
       <c r="BJ16" s="5">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>0.16666666666666666</v>
       </c>
     </row>
-    <row r="17" spans="1:62" ht="35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:62" ht="35" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="25">
         <v>9</v>
       </c>
@@ -25273,10 +25300,10 @@
         <v>1</v>
       </c>
       <c r="Q17" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R17" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S17" s="4" t="b">
         <v>0</v>
@@ -25409,10 +25436,10 @@
       </c>
       <c r="BJ17" s="5">
         <f t="shared" si="0"/>
-        <v>0.9</v>
+        <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="18" spans="1:62" ht="35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:62" ht="35" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="25">
         <v>10</v>
       </c>
@@ -25462,10 +25489,10 @@
         <v>1</v>
       </c>
       <c r="Q18" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R18" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S18" s="4" t="b">
         <v>0</v>
@@ -25598,10 +25625,10 @@
       </c>
       <c r="BJ18" s="5">
         <f t="shared" si="0"/>
-        <v>0.9</v>
+        <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="19" spans="1:62" s="10" customFormat="1" ht="35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:62" s="10" customFormat="1" ht="35" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="25">
         <v>11</v>
       </c>
@@ -25651,10 +25678,10 @@
         <v>1</v>
       </c>
       <c r="Q19" s="12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R19" s="12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S19" s="12" t="b">
         <v>0</v>
@@ -25787,10 +25814,10 @@
       </c>
       <c r="BJ19" s="13">
         <f t="shared" si="0"/>
-        <v>0.9</v>
+        <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="20" spans="1:62" ht="35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:62" ht="35" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="25">
         <v>12</v>
       </c>
@@ -25840,10 +25867,10 @@
         <v>1</v>
       </c>
       <c r="Q20" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R20" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S20" s="4" t="b">
         <v>0</v>
@@ -25976,10 +26003,10 @@
       </c>
       <c r="BJ20" s="5">
         <f t="shared" si="0"/>
-        <v>0.9</v>
+        <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="21" spans="1:62" ht="35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:62" ht="35" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="25">
         <v>13</v>
       </c>
@@ -26029,10 +26056,10 @@
         <v>1</v>
       </c>
       <c r="Q21" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R21" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S21" s="4" t="b">
         <v>0</v>
@@ -26165,7 +26192,7 @@
       </c>
       <c r="BJ21" s="5">
         <f t="shared" si="0"/>
-        <v>0.9</v>
+        <v>0.91666666666666663</v>
       </c>
     </row>
     <row r="22" spans="1:62" ht="35" customHeight="1" x14ac:dyDescent="0.2">
@@ -26354,10 +26381,10 @@
       </c>
       <c r="BJ22" s="5">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="23" spans="1:62" ht="35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:62" ht="35" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="25">
         <v>15</v>
       </c>
@@ -26407,10 +26434,10 @@
         <v>0</v>
       </c>
       <c r="Q23" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R23" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S23" s="4" t="b">
         <v>0</v>
@@ -26543,7 +26570,7 @@
       </c>
       <c r="BJ23" s="5">
         <f t="shared" si="0"/>
-        <v>0.6</v>
+        <v>0.66666666666666663</v>
       </c>
     </row>
     <row r="24" spans="1:62" ht="35" customHeight="1" x14ac:dyDescent="0.2">
@@ -26732,10 +26759,10 @@
       </c>
       <c r="BJ24" s="5">
         <f t="shared" si="0"/>
-        <v>0.3</v>
+        <v>0.25</v>
       </c>
     </row>
-    <row r="25" spans="1:62" ht="35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:62" ht="35" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="25">
         <v>17</v>
       </c>
@@ -26785,10 +26812,10 @@
         <v>1</v>
       </c>
       <c r="Q25" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R25" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S25" s="4" t="b">
         <v>0</v>
@@ -26921,10 +26948,10 @@
       </c>
       <c r="BJ25" s="5">
         <f t="shared" si="0"/>
-        <v>0.9</v>
+        <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="26" spans="1:62" ht="35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:62" ht="35" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="25">
         <v>18</v>
       </c>
@@ -26974,10 +27001,10 @@
         <v>1</v>
       </c>
       <c r="Q26" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R26" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S26" s="4" t="b">
         <v>0</v>
@@ -27110,10 +27137,10 @@
       </c>
       <c r="BJ26" s="5">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0.83333333333333337</v>
       </c>
     </row>
-    <row r="27" spans="1:62" ht="35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:62" ht="35" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="25">
         <v>19</v>
       </c>
@@ -27166,7 +27193,7 @@
         <v>0</v>
       </c>
       <c r="R27" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S27" s="4" t="b">
         <v>0</v>
@@ -27488,10 +27515,10 @@
       </c>
       <c r="BJ28" s="5">
         <f t="shared" si="0"/>
-        <v>0.3</v>
+        <v>0.25</v>
       </c>
     </row>
-    <row r="29" spans="1:62" ht="35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:62" ht="35" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="25">
         <v>21</v>
       </c>
@@ -27544,7 +27571,7 @@
         <v>0</v>
       </c>
       <c r="R29" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S29" s="4" t="b">
         <v>0</v>
@@ -27677,10 +27704,10 @@
       </c>
       <c r="BJ29" s="5">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
     </row>
-    <row r="30" spans="1:62" ht="35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:62" ht="35" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="25">
         <v>22</v>
       </c>
@@ -27730,10 +27757,10 @@
         <v>1</v>
       </c>
       <c r="Q30" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R30" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S30" s="4" t="b">
         <v>0</v>
@@ -27866,10 +27893,10 @@
       </c>
       <c r="BJ30" s="5">
         <f t="shared" si="0"/>
-        <v>0.9</v>
+        <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="31" spans="1:62" ht="35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:62" ht="35" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="25">
         <v>23</v>
       </c>
@@ -27919,10 +27946,10 @@
         <v>0</v>
       </c>
       <c r="Q31" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R31" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S31" s="4" t="b">
         <v>0</v>
@@ -28055,10 +28082,10 @@
       </c>
       <c r="BJ31" s="5">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="32" spans="1:62" ht="35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:62" ht="35" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="25">
         <v>24</v>
       </c>
@@ -28108,10 +28135,10 @@
         <v>1</v>
       </c>
       <c r="Q32" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R32" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S32" s="4" t="b">
         <v>0</v>
@@ -28244,10 +28271,10 @@
       </c>
       <c r="BJ32" s="5">
         <f t="shared" si="0"/>
-        <v>0.9</v>
+        <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="33" spans="1:64" ht="35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:64" ht="35" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="25">
         <v>25</v>
       </c>
@@ -28297,10 +28324,10 @@
         <v>1</v>
       </c>
       <c r="Q33" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R33" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S33" s="4" t="b">
         <v>0</v>
@@ -28433,10 +28460,10 @@
       </c>
       <c r="BJ33" s="5">
         <f t="shared" si="0"/>
-        <v>0.1</v>
+        <v>0.25</v>
       </c>
     </row>
-    <row r="34" spans="1:64" ht="35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:64" ht="35" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="25">
         <v>26</v>
       </c>
@@ -28486,10 +28513,10 @@
         <v>1</v>
       </c>
       <c r="Q34" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R34" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S34" s="4" t="b">
         <v>0</v>
@@ -28622,10 +28649,10 @@
       </c>
       <c r="BJ34" s="5">
         <f t="shared" si="0"/>
-        <v>0.9</v>
+        <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="35" spans="1:64" ht="35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:64" ht="35" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="25">
         <v>27</v>
       </c>
@@ -28675,10 +28702,10 @@
         <v>1</v>
       </c>
       <c r="Q35" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R35" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S35" s="4" t="b">
         <v>0</v>
@@ -28811,7 +28838,7 @@
       </c>
       <c r="BJ35" s="5">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0.58333333333333337</v>
       </c>
     </row>
     <row r="36" spans="1:64" ht="35" customHeight="1" x14ac:dyDescent="0.2">
@@ -28864,7 +28891,7 @@
         <v>0</v>
       </c>
       <c r="Q36" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R36" s="4" t="b">
         <v>0</v>
@@ -29000,7 +29027,7 @@
       </c>
       <c r="BJ36" s="5">
         <f t="shared" si="0"/>
-        <v>0.1</v>
+        <v>0.16666666666666666</v>
       </c>
     </row>
     <row r="37" spans="1:64" ht="35" customHeight="1" x14ac:dyDescent="0.2">
@@ -29189,14 +29216,14 @@
       </c>
       <c r="BJ37" s="5">
         <f t="shared" si="0"/>
-        <v>0.3</v>
+        <v>0.25</v>
       </c>
       <c r="BL37">
         <f>COUNTIF(F37:AR37,TRUE)</f>
         <v>3</v>
       </c>
     </row>
-    <row r="38" spans="1:64" ht="35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:64" ht="35" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="25">
         <v>30</v>
       </c>
@@ -29246,10 +29273,10 @@
         <v>1</v>
       </c>
       <c r="Q38" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R38" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S38" s="4" t="b">
         <v>0</v>
@@ -29382,10 +29409,10 @@
       </c>
       <c r="BJ38" s="5">
         <f t="shared" si="0"/>
-        <v>0.9</v>
+        <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="39" spans="1:64" ht="35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:64" ht="35" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="25">
         <v>31</v>
       </c>
@@ -29435,10 +29462,10 @@
         <v>1</v>
       </c>
       <c r="Q39" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R39" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S39" s="4" t="b">
         <v>0</v>
@@ -29571,10 +29598,10 @@
       </c>
       <c r="BJ39" s="5">
         <f t="shared" si="0"/>
-        <v>0.9</v>
+        <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="40" spans="1:64" ht="35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:64" ht="35" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="25">
         <v>32</v>
       </c>
@@ -29627,7 +29654,7 @@
         <v>0</v>
       </c>
       <c r="R40" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S40" s="4" t="b">
         <v>0</v>
@@ -29760,7 +29787,7 @@
       </c>
       <c r="BJ40" s="5">
         <f t="shared" si="0"/>
-        <v>0.9</v>
+        <v>0.83333333333333337</v>
       </c>
     </row>
     <row r="41" spans="1:64" ht="35" customHeight="1" x14ac:dyDescent="0.2">
@@ -29813,7 +29840,7 @@
         <v>0</v>
       </c>
       <c r="Q41" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R41" s="4" t="b">
         <v>0</v>
@@ -29949,14 +29976,14 @@
       </c>
       <c r="BJ41" s="5">
         <f t="shared" si="0"/>
-        <v>0.6</v>
+        <v>0.58333333333333337</v>
       </c>
       <c r="BL41">
         <f>COUNTIF(F41:BI41,TRUE)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
-    <row r="42" spans="1:64" ht="35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:64" ht="35" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="25">
         <v>34</v>
       </c>
@@ -30006,10 +30033,10 @@
         <v>1</v>
       </c>
       <c r="Q42" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R42" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S42" s="4" t="b">
         <v>0</v>
@@ -30142,10 +30169,10 @@
       </c>
       <c r="BJ42" s="5">
         <f t="shared" si="0"/>
-        <v>0.7</v>
+        <v>0.75</v>
       </c>
     </row>
-    <row r="43" spans="1:64" ht="35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:64" ht="35" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="25">
         <v>35</v>
       </c>
@@ -30195,10 +30222,10 @@
         <v>1</v>
       </c>
       <c r="Q43" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R43" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S43" s="4" t="b">
         <v>0</v>
@@ -30331,10 +30358,10 @@
       </c>
       <c r="BJ43" s="5">
         <f t="shared" si="0"/>
-        <v>0.7</v>
+        <v>0.75</v>
       </c>
     </row>
-    <row r="44" spans="1:64" ht="35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:64" ht="35" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="25">
         <v>36</v>
       </c>
@@ -30384,10 +30411,10 @@
         <v>1</v>
       </c>
       <c r="Q44" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R44" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S44" s="4" t="b">
         <v>0</v>
@@ -30520,10 +30547,10 @@
       </c>
       <c r="BJ44" s="5">
         <f t="shared" si="0"/>
-        <v>0.9</v>
+        <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="45" spans="1:64" ht="35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:64" ht="35" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="25">
         <v>37</v>
       </c>
@@ -30573,10 +30600,10 @@
         <v>0</v>
       </c>
       <c r="Q45" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R45" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S45" s="4" t="b">
         <v>0</v>
@@ -30709,10 +30736,10 @@
       </c>
       <c r="BJ45" s="5">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0.83333333333333337</v>
       </c>
     </row>
-    <row r="46" spans="1:64" ht="35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:64" ht="35" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="25">
         <v>38</v>
       </c>
@@ -30762,10 +30789,10 @@
         <v>1</v>
       </c>
       <c r="Q46" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R46" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S46" s="4" t="b">
         <v>0</v>
@@ -30898,10 +30925,10 @@
       </c>
       <c r="BJ46" s="5">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0.83333333333333337</v>
       </c>
     </row>
-    <row r="47" spans="1:64" ht="35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:64" ht="35" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="25">
         <v>39</v>
       </c>
@@ -30951,10 +30978,10 @@
         <v>1</v>
       </c>
       <c r="Q47" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R47" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S47" s="4" t="b">
         <v>0</v>
@@ -31087,10 +31114,10 @@
       </c>
       <c r="BJ47" s="5">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0.58333333333333337</v>
       </c>
     </row>
-    <row r="48" spans="1:64" ht="35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:64" ht="35" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="25">
         <v>40</v>
       </c>
@@ -31140,10 +31167,10 @@
         <v>0</v>
       </c>
       <c r="Q48" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R48" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S48" s="4" t="b">
         <v>0</v>
@@ -31276,7 +31303,7 @@
       </c>
       <c r="BJ48" s="5">
         <f t="shared" si="0"/>
-        <v>0.7</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="49" spans="1:64" ht="35" customHeight="1" x14ac:dyDescent="0.2">
@@ -31468,7 +31495,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:64" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:64" ht="40" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="25">
         <v>42</v>
       </c>
@@ -31518,10 +31545,10 @@
         <v>1</v>
       </c>
       <c r="Q50" s="8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R50" s="8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S50" s="8" t="b">
         <v>0</v>
@@ -31654,11 +31681,11 @@
       </c>
       <c r="BJ50" s="9">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="BL50">
         <f>COUNTIF(F50:BI50,TRUE)</f>
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="51" spans="1:64" ht="90" x14ac:dyDescent="0.2">
@@ -31847,10 +31874,10 @@
       </c>
       <c r="BJ51" s="9">
         <f t="shared" si="0"/>
-        <v>0.4</v>
+        <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="52" spans="1:64" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:64" hidden="1" x14ac:dyDescent="0.2">
       <c r="F52">
         <f t="shared" ref="F52:BI52" si="1">COUNTIF(F9:F50, TRUE)</f>
         <v>0</v>
@@ -31889,7 +31916,7 @@
       </c>
       <c r="O52">
         <f t="shared" si="1"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P52">
         <f t="shared" si="1"/>
@@ -31897,11 +31924,11 @@
       </c>
       <c r="Q52">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="R52">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="S52">
         <f t="shared" si="1"/>
@@ -32076,7 +32103,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:64" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:64" hidden="1" x14ac:dyDescent="0.2">
       <c r="F53">
         <f t="shared" ref="F53:BI53" si="2">COUNTIF(F9:F50, FALSE)</f>
         <v>42</v>
@@ -32115,7 +32142,7 @@
       </c>
       <c r="O53">
         <f t="shared" si="2"/>
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="P53">
         <f t="shared" si="2"/>
@@ -32123,11 +32150,11 @@
       </c>
       <c r="Q53">
         <f t="shared" si="2"/>
-        <v>42</v>
+        <v>11</v>
       </c>
       <c r="R53">
         <f t="shared" si="2"/>
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="S53">
         <f t="shared" si="2"/>
@@ -32344,6 +32371,11 @@
   </sheetData>
   <autoFilter ref="A7:BJ53" xr:uid="{B41F0606-7A76-1E43-969A-749A897BA916}">
     <filterColumn colId="1" showButton="0"/>
+    <filterColumn colId="17">
+      <filters>
+        <filter val="FALSE"/>
+      </filters>
+    </filterColumn>
   </autoFilter>
   <mergeCells count="7">
     <mergeCell ref="B7:C7"/>
